--- a/docs/gara-appalto/SOC-RISPOSTE-PREFILTRATE-v2.xlsx
+++ b/docs/gara-appalto/SOC-RISPOSTE-PREFILTRATE-v2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Risposte Aggiornate" sheetId="1" r:id="rId1"/>
+    <sheet name="SOC Risposte W3Suite" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,14 +397,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:E12"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="120.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -423,9 +422,6 @@
       <c r="E1" t="str">
         <v>P - Short Answer</v>
       </c>
-      <c r="F1" t="str">
-        <v>Q - Non Compliance</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -441,10 +437,7 @@
         <v>Full</v>
       </c>
       <c r="E2" t="str">
-        <v>Autenticazione OAuth2/OIDC nativa. Architettura predisposta per federazione SAML 2.0/OIDC con IdP esterni. Integrazione con Azure AD W3 configurabile in fase di onboarding progetto. SSO enterprise supportato.</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
+        <v>Autenticazione OAuth2/OIDC nativa tramite Identity &amp; Auth Service dedicato. Architettura predisposta per federazione SAML 2.0/OIDC con IdP esterni (es. Azure AD W3). SSO enterprise configurabile in fase di onboarding. SLA: 99.9%, RTO &lt;5 min.</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +454,7 @@
         <v>Full</v>
       </c>
       <c r="E3" t="str">
-        <v>RBAC gerarchico implementato a 3 livelli (Tenant→Role→User) con 200+ permessi granulari. Row-Level Security PostgreSQL per isolamento dati multi-tenant. Profili funzione configurabili per dominio di business.</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
+        <v>RBAC gerarchico implementato a 3 livelli (Tenant→Role→User) con 200+ permessi granulari. Row-Level Security PostgreSQL (SLA 99.9%) per isolamento dati multi-tenant. Profili funzione configurabili per dominio di business.</v>
       </c>
     </row>
     <row r="4">
@@ -481,10 +471,7 @@
         <v>Full</v>
       </c>
       <c r="E4" t="str">
-        <v>API REST implementate per gestione utenti (creazione, modifica, disattivazione). Supporto bulk import. Webhook configurabili per sincronizzazione con sistemi esterni. Documentazione OpenAPI disponibile.</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
+        <v>API REST implementate per gestione utenti (creazione, modifica, disattivazione). Supporto bulk import. Webhook configurabili per sincronizzazione con sistemi esterni. Documentazione OpenAPI disponibile. Backend Node.js con SLA 99.9%.</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +479,7 @@
         <v>Design GL # 13</v>
       </c>
       <c r="B5" t="str">
-        <v>CORE PLATFORM</v>
+        <v>CORE PLATFORM, DATABASE LAYER</v>
       </c>
       <c r="C5" t="str">
         <v>Yes</v>
@@ -501,10 +488,7 @@
         <v>Full</v>
       </c>
       <c r="E5" t="str">
-        <v>Encryption secrets implementata con AES-256-GCM at-rest. Gestione centralizzata chiavi con accesso role-based e audit trail. Architettura predisposta per integrazione con secret manager esterni (Vault).</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
+        <v>Encryption secrets implementata con AES-256-GCM at-rest tramite Secret Manager dedicato. Gestione centralizzata chiavi con accesso role-based e audit trail. Architettura predisposta per integrazione con HashiCorp Vault. Backup encrypted daily.</v>
       </c>
     </row>
     <row r="6">
@@ -521,10 +505,7 @@
         <v>Full</v>
       </c>
       <c r="E6" t="str">
-        <v>Admin portal con autenticazione OAuth2/OIDC. Architettura predisposta per federazione con IdP W3 (Azure AD). Segregazione ruoli admin implementata: Platform Admin, Tenant Admin, App Admin Jean.</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
+        <v>Admin portal con autenticazione OAuth2/OIDC via Identity &amp; Auth Service. Architettura predisposta per federazione con IdP W3 (Azure AD). Segregazione ruoli admin implementata: Platform Admin, Tenant Admin, DB Admin. SLA 99.9%.</v>
       </c>
     </row>
     <row r="7">
@@ -541,10 +522,7 @@
         <v>Full</v>
       </c>
       <c r="E7" t="str">
-        <v>Ruoli admin definiti e documentati: Platform Admin (infrastruttura), Tenant Admin (configurazione), DB Admin (database). RBAC granulare per ogni risorsa. Principio Least Privilege applicato.</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
+        <v>Ruoli admin definiti e documentati: Platform Admin (infrastruttura), Tenant Admin (configurazione), DB Admin (database). RBAC granulare per ogni risorsa. Principio Least Privilege applicato. PostgreSQL Primary/Replica con SLA 99.9%.</v>
       </c>
     </row>
     <row r="8">
@@ -561,10 +539,7 @@
         <v>Full</v>
       </c>
       <c r="E8" t="str">
-        <v>Accesso VM via SSH con autenticazione key-based. Architettura integrabile con soluzione PAM W3. Audit log completo per ogni accesso. Fortinet per network access control.</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
+        <v>Accesso VM via SSH con autenticazione key-based. Architettura integrabile con soluzione PAM W3 (es. CyberArk, Teleport). Audit Logging Service attivo per ogni accesso (retention 90 giorni). Fortinet FortiGate per network access control.</v>
       </c>
     </row>
     <row r="9">
@@ -581,10 +556,7 @@
         <v>Full</v>
       </c>
       <c r="E9" t="str">
-        <v>Comunicazioni M2M via OAuth2 Client Credentials flow per service accounts. API Key con scoping per dominio. TLS 1.3 obbligatorio per tutte le comunicazioni. mTLS attivabile su richiesta.</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
+        <v>Comunicazioni M2M via OAuth2 Client Credentials flow per service accounts. API Key con scoping per dominio. TLS 1.3 obbligatorio (Nginx Reverse Proxy SLA 99.9%). mTLS attivabile su richiesta per comunicazioni inter-service.</v>
       </c>
     </row>
     <row r="10">
@@ -601,10 +573,7 @@
         <v>Full</v>
       </c>
       <c r="E10" t="str">
-        <v>Security implementata: TLS 1.3, JWT validation, rate limiting, input sanitization, audit logging strutturato. WAF Fortinet per protezione perimetrale. Standard security W3 applicabili.</v>
-      </c>
-      <c r="F10" t="str">
-        <v/>
+        <v>Security implementata: TLS 1.3, JWT validation, rate limiting, input sanitization. Audit Logging Service strutturato con retention 90 giorni. WAF Fortinet FortiGate (SLA 99.9%) per protezione perimetrale. Standard security W3 applicabili.</v>
       </c>
     </row>
     <row r="11">
@@ -621,10 +590,7 @@
         <v>Full</v>
       </c>
       <c r="E11" t="str">
-        <v>Hosting su Seeweb Italia con Fortinet FortiGate firewall. Accesso solo HTTPS (443). IP whitelisting per accessi admin. IPS/IDS attivo. Regole firewall documentate e modificabili su richiesta W3.</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
+        <v>Hosting su Seeweb Italia (ISO 27001) con Fortinet FortiGate firewall (Active-Passive, SLA 99.9%). Accesso solo HTTPS (443). IP whitelisting per accessi admin. IPS/IDS attivo. Regole firewall documentate e modificabili su richiesta W3.</v>
       </c>
     </row>
     <row r="12">
@@ -641,15 +607,12 @@
         <v>Full</v>
       </c>
       <c r="E12" t="str">
-        <v>CI/CD pipeline con security checks: analisi dipendenze (npm audit), code review, test automatici pre-deploy. Architettura predisposta per integrazione tool SAST/DAST. Report sicurezza disponibili.</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
+        <v>CI/CD pipeline con security checks: analisi dipendenze (npm audit), code review, test automatici pre-deploy. Architettura predisposta per integrazione tool SAST/DAST (Semgrep, Trivy). GitOps deploy. AI Services con SLA 99.5% (OpenAI) e 99.9% (AI Gateway).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
 </file>